--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-04-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-04-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BTS Arirang</v>
+        <v>ריי – This Music May Contain Hope</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/bts-arirang/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%99%d7%99-this-music-may-contain-hope/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום Arirang של BTS (שיצא במרץ 2026) הפך בתוך שבועות ספורים לאחד התקליטים המבוקשים בעולם גם פיזית (ויניל/מהדורות אספנים) וגם סטרימינג, וזה לא במקרה. מדובר בשילוב נדיר של אירוע תרבותי, מהלך מוזיקלי מחושב, ורגע רגשי של קאמבק. בעיני המעריצים, זה</v>
+        <v>האלבום "This Music May Contain Hope" של  ריי RAYE הוא יצירה טעונה רגשית, שממשיכה את הקו האישי והחשוף שהיא ביססה מאז הפריצה העצמאית שלה. כבר בשם יש פרובוקציה עדינה: במקום אזהרה שלילית (“עלול להכיל תכנים קשים”), היא מציעה אפשרות הפוכה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>BTS Arirang</v>
+        <v>ריי – This Music May Contain Hope</v>
       </c>
     </row>
   </sheetData>
